--- a/AZ-900_Reference.xlsx
+++ b/AZ-900_Reference.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="READ ME" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="MC (with source + answer)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="True-False (with source)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Yes-No (with source)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Original Use-Case Answers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Redundant Questions" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Source Map" sheetId="6" state="visible" r:id="rId6"/>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B26"/>
+  <dimension ref="B1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. AZ-900_Kahoot_TrueFalse.xlsx       -&gt; import as a second kahoot (True/False questions).</t>
+          <t xml:space="preserve">  2. AZ-900_Kahoot_YesNo.xlsx           -&gt; import as a second kahoot (Yes/No statements).</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Correct answer column uses option NUMBERS (1-4). For True/False: 1 = True, 2 = False.</t>
+          <t xml:space="preserve">  Correct answer column uses option NUMBERS (1-4). For Yes/No: 1 = Yes, 2 = No.</t>
         </is>
       </c>
     </row>
@@ -569,59 +569,76 @@
       <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>THIS REFERENCE WORKBOOK CONTAINS:</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>YES/NO CATEGORY: For each statement, choose Yes if it is TRUE, otherwise No.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 'MC (with source + answer)'  : every multiple-choice question, its correct answer, and the PDF source.</t>
+          <t xml:space="preserve">  (This replaces the old True/False wording: Yes = True, No = False.)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 'True-False (with source)'   : every True/False statement, the answer, and the PDF source.</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 'Original Use-Case Answers'  : the open-ended answers exactly as stated in the PDFs (for study).</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>THIS REFERENCE WORKBOOK CONTAINS:</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 'Redundant Questions'        : duplicate concepts to avoid repeating.</t>
+          <t xml:space="preserve">  - 'MC (with source + answer)'  : every multiple-choice question, its correct answer, and the PDF source.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 'Source Map'                 : which PDF each block came from.</t>
+          <t xml:space="preserve">  - 'Yes-No (with source)'       : every Yes/No statement, the answer, and the PDF source.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 'Original Use-Case Answers'  : the open-ended answers exactly as stated in the PDFs (for study).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>INTEGRITY: every question and answer comes strictly from the 3 PDFs. Wrong MC options are real</t>
+          <t xml:space="preserve">  - 'Redundant Questions'        : duplicate concepts to avoid repeating.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 'Source Map'                 : which PDF each block came from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>INTEGRITY: every question and answer comes strictly from the 3 PDFs. Wrong MC options are real</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Azure terms drawn from those same PDFs, used only as distractors - no facts were invented.</t>
         </is>
@@ -5266,7 +5283,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -5283,7 +5300,7 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Answer (Yes/No)</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
@@ -5303,7 +5320,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -5323,7 +5340,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -5343,7 +5360,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -5363,7 +5380,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -5383,7 +5400,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -5403,7 +5420,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -5423,7 +5440,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -5443,7 +5460,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -5463,7 +5480,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -5483,7 +5500,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -5503,7 +5520,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -5523,7 +5540,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -5543,7 +5560,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -5563,7 +5580,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -5583,7 +5600,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -5603,7 +5620,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -5623,7 +5640,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -5643,7 +5660,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -5663,7 +5680,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -5683,7 +5700,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -5703,7 +5720,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -5723,7 +5740,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -5743,7 +5760,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -5763,7 +5780,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -5783,7 +5800,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -5803,7 +5820,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -5823,7 +5840,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -5843,7 +5860,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -5863,7 +5880,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -5883,7 +5900,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -5903,7 +5920,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -5923,7 +5940,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -5943,7 +5960,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -5963,7 +5980,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -5983,7 +6000,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -6003,7 +6020,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
